--- a/enlaces/enlaces.xlsx
+++ b/enlaces/enlaces.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mi unidad\CH_projects\SDIS\Gestion de conocimiento\gestor-conocimiento-2025\enlaces\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mi unidad\CH_projects\SDIS\Gestion de conocimiento\gestor-conocimiento\enlaces\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{541672A2-1797-4F36-BEFE-670EB4C74FA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2A097D0-7CB8-4407-9698-307803BAC391}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="instrucciones" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="266">
   <si>
     <t>ARCHIVO</t>
   </si>
@@ -791,6 +791,36 @@
   </si>
   <si>
     <t>2023-10-11</t>
+  </si>
+  <si>
+    <t>https://sdisgovco.sharepoint.com/:w:/r/sites/SubdireccindeJuventudPoliticaPblica/Documentos%20compartidos/Anal%C3%ADtica%20e%20Innovaci%C3%B3n/Gestor%20de%20conocimiento/enlaces/Documentaci%C3%B3n%20JCO/02_JCO_instructivo_pago/20240308_ins_pss_125_v0_instructivo_pagos_parceros.docx?d=wd102df19a9164946a456beea1927b4da&amp;csf=1&amp;web=1&amp;e=sp7lh2</t>
+  </si>
+  <si>
+    <t>https://sdisgovco.sharepoint.com/:b:/r/sites/SubdireccindeJuventudPoliticaPblica/Documentos%20compartidos/Anal%C3%ADtica%20e%20Innovaci%C3%B3n/Gestor%20de%20conocimiento/enlaces/Documentaci%C3%B3n%20JCO/07_Parceros_convenios/convenio_10907_2021/000.%20Estudios%20Previos%20IDIPRON%20-%20SDIS_REVPOB.pdf?csf=1&amp;web=1&amp;e=i1m9Wz</t>
+  </si>
+  <si>
+    <t>https://sdisgovco.sharepoint.com/:b:/r/sites/SubdireccindeJuventudPoliticaPblica/Documentos%20compartidos/Anal%C3%ADtica%20e%20Innovaci%C3%B3n/Gestor%20de%20conocimiento/enlaces/Documentaci%C3%B3n%20JCO/07_Parceros_convenios/convenio_10907_2021/004.%20Minuta%20Convenio.pdf?csf=1&amp;web=1&amp;e=rNXqhi</t>
+  </si>
+  <si>
+    <t>https://sdisgovco.sharepoint.com/:b:/r/sites/SubdireccindeJuventudPoliticaPblica/Documentos%20compartidos/Anal%C3%ADtica%20e%20Innovaci%C3%B3n/Gestor%20de%20conocimiento/enlaces/Documentaci%C3%B3n%20JCO/07_Parceros_convenios/convenio_10907_2021/001.%20Anexo%20Tecnico%20Convenio%2010907-2021.pdf?csf=1&amp;web=1&amp;e=JY3rCR</t>
+  </si>
+  <si>
+    <t>https://sdisgovco.sharepoint.com/:b:/r/sites/SubdireccindeJuventudPoliticaPblica/Documentos%20compartidos/Anal%C3%ADtica%20e%20Innovaci%C3%B3n/Gestor%20de%20conocimiento/enlaces/Documentaci%C3%B3n%20JCO/07_Parceros_convenios/convenio_5714_2023/C_PROCESO_23-22-62415_01002009_118807585.pdf?csf=1&amp;web=1&amp;e=LoGhSz</t>
+  </si>
+  <si>
+    <t>https://sdisgovco.sharepoint.com/:b:/r/sites/SubdireccindeJuventudPoliticaPblica/Documentos%20compartidos/Anal%C3%ADtica%20e%20Innovaci%C3%B3n/Gestor%20de%20conocimiento/enlaces/Documentaci%C3%B3n%20JCO/07_Parceros_convenios/convenio_8336_2021/ALUMA_PROCESO_21-22-26707_01002009_130655716.pdf?csf=1&amp;web=1&amp;e=JgNTkN</t>
+  </si>
+  <si>
+    <t>https://sdisgovco.sharepoint.com/:b:/r/sites/SubdireccindeJuventudPoliticaPblica/Documentos%20compartidos/Anal%C3%ADtica%20e%20Innovaci%C3%B3n/Gestor%20de%20conocimiento/enlaces/Documentaci%C3%B3n%20JCO/07_Parceros_convenios/convenio_8336_2021/C_PROCESO_21-22-26707_01002009_90251312.pdf?csf=1&amp;web=1&amp;e=MTsOli</t>
+  </si>
+  <si>
+    <t>https://sdisgovco.sharepoint.com/:b:/r/sites/SubdireccindeJuventudPoliticaPblica/Documentos%20compartidos/Anal%C3%ADtica%20e%20Innovaci%C3%B3n/Gestor%20de%20conocimiento/enlaces/Documentaci%C3%B3n%20JCO/08_Parceros_mesa_GIS/%2310%20ACTA%20MESA%20GIS%2013102022.Firmado.pdf?csf=1&amp;web=1&amp;e=dzUZ3a</t>
+  </si>
+  <si>
+    <t>https://sdisgovco.sharepoint.com/:b:/r/sites/SubdireccindeJuventudPoliticaPblica/Documentos%20compartidos/Anal%C3%ADtica%20e%20Innovaci%C3%B3n/Gestor%20de%20conocimiento/enlaces/Documentaci%C3%B3n%20JCO/08_Parceros_mesa_GIS/ACTA%20Mesa%20GIs%2014092021.pdf?csf=1&amp;web=1&amp;e=uEBfrO</t>
+  </si>
+  <si>
+    <t>https://sdisgovco.sharepoint.com/:b:/r/sites/SubdireccindeJuventudPoliticaPblica/Documentos%20compartidos/Anal%C3%ADtica%20e%20Innovaci%C3%B3n/Gestor%20de%20conocimiento/enlaces/Documentaci%C3%B3n%20JCO/08_Parceros_mesa_GIS/ACTA%20MESA%20GIS%20no.%203%2011-OCT-23.pdf?csf=1&amp;web=1&amp;e=aELNxY</t>
   </si>
 </sst>
 </file>
@@ -848,7 +878,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -863,6 +893,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF8F4E1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -894,7 +936,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -934,6 +976,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1238,334 +1284,334 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A75"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:1" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
     </row>
-    <row r="6" spans="1:1" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:1" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
     </row>
-    <row r="13" spans="1:1" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:1" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
     </row>
-    <row r="24" spans="1:1" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:1" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4"/>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="3"/>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="3"/>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="3"/>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="3"/>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="3"/>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="3"/>
     </row>
-    <row r="54" spans="1:1" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:1" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="4"/>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="3"/>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" s="3"/>
     </row>
-    <row r="63" spans="1:1" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:1" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="4"/>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" s="3"/>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="3"/>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" s="3"/>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" s="3"/>
     </row>
-    <row r="74" spans="1:1" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:1" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="4"/>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
         <v>68</v>
       </c>
@@ -1577,15 +1623,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:C21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="81.265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="255.59765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="81.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="255.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>69</v>
       </c>
@@ -1596,212 +1642,223 @@
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="15" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A3" s="6" t="s">
+    <row r="3" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="15" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A4" s="6" t="s">
+    <row r="4" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="17" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A5" s="6" t="s">
+    <row r="5" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="17" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A6" s="6" t="s">
+    <row r="6" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="17" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A7" s="6" t="s">
+    <row r="7" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="17" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A8" s="6" t="s">
+    <row r="8" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="17" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A9" s="6" t="s">
+    <row r="9" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="17" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A10" s="6" t="s">
+    <row r="10" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="17" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A11" s="6" t="s">
+    <row r="11" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="17" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A12" s="6" t="s">
+    <row r="12" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="17" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A13" s="6" t="s">
+    <row r="13" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="17" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A14" s="6" t="s">
+    <row r="14" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="17" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A15" s="6" t="s">
+    <row r="15" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="15" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A16" s="6" t="s">
+    <row r="16" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="15" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A17" s="6" t="s">
+    <row r="17" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="15" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A18" s="6" t="s">
+    <row r="18" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="15" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A19" s="6" t="s">
+    <row r="19" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="15" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
+    <row r="20" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="17" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="C21" s="17" t="s">
         <v>110</v>
       </c>
     </row>
@@ -1816,16 +1873,16 @@
     <tabColor theme="7" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:G57"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="48" customWidth="1"/>
+    <col min="2" max="2" width="50.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="120.265625" customWidth="1"/>
-    <col min="6" max="6" width="13.265625" customWidth="1"/>
+    <col min="4" max="4" width="120.28515625" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>111</v>
       </c>
@@ -1848,7 +1905,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>118</v>
       </c>
@@ -1867,7 +1924,7 @@
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
     </row>
-    <row r="3" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
         <v>118</v>
       </c>
@@ -1886,7 +1943,7 @@
       <c r="F3" s="8"/>
       <c r="G3" s="8"/>
     </row>
-    <row r="4" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>126</v>
       </c>
@@ -1896,14 +1953,14 @@
       <c r="C4" t="s">
         <v>128</v>
       </c>
-      <c r="D4" t="s">
-        <v>129</v>
+      <c r="D4" s="13" t="s">
+        <v>256</v>
       </c>
       <c r="F4" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="5" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>126</v>
       </c>
@@ -1922,7 +1979,7 @@
       <c r="F5" s="8"/>
       <c r="G5" s="8"/>
     </row>
-    <row r="6" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
         <v>126</v>
       </c>
@@ -1941,7 +1998,7 @@
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
     </row>
-    <row r="7" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
         <v>126</v>
       </c>
@@ -1960,7 +2017,7 @@
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
     </row>
-    <row r="8" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>136</v>
       </c>
@@ -1979,7 +2036,7 @@
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
     </row>
-    <row r="9" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
         <v>136</v>
       </c>
@@ -1998,7 +2055,7 @@
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
     </row>
-    <row r="10" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
         <v>136</v>
       </c>
@@ -2017,7 +2074,7 @@
       <c r="F10" s="8"/>
       <c r="G10" s="8"/>
     </row>
-    <row r="11" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
         <v>136</v>
       </c>
@@ -2036,7 +2093,7 @@
       <c r="F11" s="8"/>
       <c r="G11" s="8"/>
     </row>
-    <row r="12" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
         <v>136</v>
       </c>
@@ -2055,7 +2112,7 @@
       <c r="F12" s="8"/>
       <c r="G12" s="8"/>
     </row>
-    <row r="13" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
         <v>136</v>
       </c>
@@ -2074,7 +2131,7 @@
       <c r="F13" s="8"/>
       <c r="G13" s="8"/>
     </row>
-    <row r="14" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>136</v>
       </c>
@@ -2093,7 +2150,7 @@
       <c r="F14" s="8"/>
       <c r="G14" s="8"/>
     </row>
-    <row r="15" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
         <v>136</v>
       </c>
@@ -2112,7 +2169,7 @@
       <c r="F15" s="8"/>
       <c r="G15" s="8"/>
     </row>
-    <row r="16" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>154</v>
       </c>
@@ -2131,7 +2188,7 @@
       </c>
       <c r="G16" s="8"/>
     </row>
-    <row r="17" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
         <v>154</v>
       </c>
@@ -2150,7 +2207,7 @@
       </c>
       <c r="G17" s="8"/>
     </row>
-    <row r="18" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
         <v>154</v>
       </c>
@@ -2169,7 +2226,7 @@
       </c>
       <c r="G18" s="8"/>
     </row>
-    <row r="19" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
         <v>163</v>
       </c>
@@ -2188,7 +2245,7 @@
       </c>
       <c r="G19" s="8"/>
     </row>
-    <row r="20" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
         <v>163</v>
       </c>
@@ -2207,7 +2264,7 @@
       </c>
       <c r="G20" s="8"/>
     </row>
-    <row r="21" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
         <v>163</v>
       </c>
@@ -2226,7 +2283,7 @@
       </c>
       <c r="G21" s="8"/>
     </row>
-    <row r="22" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
         <v>163</v>
       </c>
@@ -2245,7 +2302,7 @@
       </c>
       <c r="G22" s="8"/>
     </row>
-    <row r="23" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
         <v>163</v>
       </c>
@@ -2264,7 +2321,7 @@
       </c>
       <c r="G23" s="8"/>
     </row>
-    <row r="24" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
         <v>163</v>
       </c>
@@ -2283,7 +2340,7 @@
       </c>
       <c r="G24" s="8"/>
     </row>
-    <row r="25" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
         <v>163</v>
       </c>
@@ -2302,7 +2359,7 @@
       </c>
       <c r="G25" s="8"/>
     </row>
-    <row r="26" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
         <v>163</v>
       </c>
@@ -2321,7 +2378,7 @@
       </c>
       <c r="G26" s="8"/>
     </row>
-    <row r="27" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
         <v>163</v>
       </c>
@@ -2340,7 +2397,7 @@
       </c>
       <c r="G27" s="8"/>
     </row>
-    <row r="28" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
         <v>163</v>
       </c>
@@ -2359,7 +2416,7 @@
       <c r="F28" s="8"/>
       <c r="G28" s="8"/>
     </row>
-    <row r="29" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
         <v>163</v>
       </c>
@@ -2378,7 +2435,7 @@
       <c r="F29" s="8"/>
       <c r="G29" s="8"/>
     </row>
-    <row r="30" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
         <v>163</v>
       </c>
@@ -2397,7 +2454,7 @@
       <c r="F30" s="8"/>
       <c r="G30" s="8"/>
     </row>
-    <row r="31" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
         <v>163</v>
       </c>
@@ -2416,7 +2473,7 @@
       <c r="F31" s="8"/>
       <c r="G31" s="8"/>
     </row>
-    <row r="32" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
         <v>163</v>
       </c>
@@ -2435,7 +2492,7 @@
       <c r="F32" s="8"/>
       <c r="G32" s="8"/>
     </row>
-    <row r="33" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
         <v>163</v>
       </c>
@@ -2454,7 +2511,7 @@
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
     </row>
-    <row r="34" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
         <v>163</v>
       </c>
@@ -2473,7 +2530,7 @@
       <c r="F34" s="8"/>
       <c r="G34" s="8"/>
     </row>
-    <row r="35" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
         <v>163</v>
       </c>
@@ -2492,7 +2549,7 @@
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
     </row>
-    <row r="36" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
         <v>163</v>
       </c>
@@ -2511,7 +2568,7 @@
       <c r="F36" s="8"/>
       <c r="G36" s="8"/>
     </row>
-    <row r="37" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
         <v>163</v>
       </c>
@@ -2530,7 +2587,7 @@
       <c r="F37" s="8"/>
       <c r="G37" s="8"/>
     </row>
-    <row r="38" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="12" t="s">
         <v>163</v>
       </c>
@@ -2549,7 +2606,7 @@
       <c r="F38" s="8"/>
       <c r="G38" s="8"/>
     </row>
-    <row r="39" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="12" t="s">
         <v>163</v>
       </c>
@@ -2568,7 +2625,7 @@
       <c r="F39" s="8"/>
       <c r="G39" s="8"/>
     </row>
-    <row r="40" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
         <v>163</v>
       </c>
@@ -2587,7 +2644,7 @@
       <c r="F40" s="8"/>
       <c r="G40" s="8"/>
     </row>
-    <row r="41" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
         <v>163</v>
       </c>
@@ -2606,7 +2663,7 @@
       <c r="F41" s="8"/>
       <c r="G41" s="8"/>
     </row>
-    <row r="42" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="12" t="s">
         <v>163</v>
       </c>
@@ -2625,7 +2682,7 @@
       <c r="F42" s="8"/>
       <c r="G42" s="8"/>
     </row>
-    <row r="43" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
         <v>163</v>
       </c>
@@ -2644,7 +2701,7 @@
       <c r="F43" s="8"/>
       <c r="G43" s="8"/>
     </row>
-    <row r="44" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
         <v>163</v>
       </c>
@@ -2663,7 +2720,7 @@
       <c r="F44" s="8"/>
       <c r="G44" s="8"/>
     </row>
-    <row r="45" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="12" t="s">
         <v>231</v>
       </c>
@@ -2682,7 +2739,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="46" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="12" t="s">
         <v>231</v>
       </c>
@@ -2701,7 +2758,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="47" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="12" t="s">
         <v>231</v>
       </c>
@@ -2720,7 +2777,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="12" t="s">
         <v>231</v>
       </c>
@@ -2739,7 +2796,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
         <v>242</v>
       </c>
@@ -2749,14 +2806,16 @@
       <c r="C49" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="D49" s="6"/>
+      <c r="D49" s="13" t="s">
+        <v>261</v>
+      </c>
       <c r="E49" s="6"/>
       <c r="F49" s="14" t="s">
         <v>122</v>
       </c>
       <c r="G49" s="6"/>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
         <v>242</v>
       </c>
@@ -2766,14 +2825,16 @@
       <c r="C50" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="D50" s="6"/>
+      <c r="D50" s="13" t="s">
+        <v>262</v>
+      </c>
       <c r="E50" s="6"/>
       <c r="F50" s="14" t="s">
         <v>122</v>
       </c>
       <c r="G50" s="6"/>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
         <v>242</v>
       </c>
@@ -2783,14 +2844,16 @@
       <c r="C51" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="D51" s="6"/>
+      <c r="D51" s="13" t="s">
+        <v>257</v>
+      </c>
       <c r="E51" s="6"/>
       <c r="F51" s="14" t="s">
         <v>122</v>
       </c>
       <c r="G51" s="6"/>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
         <v>242</v>
       </c>
@@ -2800,14 +2863,16 @@
       <c r="C52" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="D52" s="6"/>
+      <c r="D52" s="13" t="s">
+        <v>259</v>
+      </c>
       <c r="E52" s="6"/>
       <c r="F52" s="14" t="s">
         <v>122</v>
       </c>
       <c r="G52" s="6"/>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
         <v>242</v>
       </c>
@@ -2817,14 +2882,16 @@
       <c r="C53" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="D53" s="6"/>
+      <c r="D53" s="13" t="s">
+        <v>258</v>
+      </c>
       <c r="E53" s="6"/>
       <c r="F53" s="14" t="s">
         <v>122</v>
       </c>
       <c r="G53" s="6"/>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
         <v>242</v>
       </c>
@@ -2834,14 +2901,16 @@
       <c r="C54" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="D54" s="6"/>
+      <c r="D54" s="13" t="s">
+        <v>260</v>
+      </c>
       <c r="E54" s="6"/>
       <c r="F54" s="14" t="s">
         <v>122</v>
       </c>
       <c r="G54" s="6"/>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
         <v>249</v>
       </c>
@@ -2851,14 +2920,16 @@
       <c r="C55" s="8" t="s">
         <v>251</v>
       </c>
-      <c r="D55" s="6"/>
+      <c r="D55" s="13" t="s">
+        <v>264</v>
+      </c>
       <c r="E55" s="6"/>
       <c r="F55" s="14" t="s">
         <v>122</v>
       </c>
       <c r="G55" s="6"/>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
         <v>249</v>
       </c>
@@ -2868,14 +2939,16 @@
       <c r="C56" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="D56" s="6"/>
+      <c r="D56" s="13" t="s">
+        <v>263</v>
+      </c>
       <c r="E56" s="6"/>
       <c r="F56" s="14" t="s">
         <v>122</v>
       </c>
       <c r="G56" s="6"/>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
         <v>249</v>
       </c>
@@ -2885,7 +2958,9 @@
       <c r="C57" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="D57" s="6"/>
+      <c r="D57" s="13" t="s">
+        <v>265</v>
+      </c>
       <c r="E57" s="6"/>
       <c r="F57" s="14" t="s">
         <v>122</v>
@@ -2896,50 +2971,59 @@
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
     <hyperlink ref="D3" r:id="rId2" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
-    <hyperlink ref="D4" r:id="rId3" xr:uid="{00000000-0004-0000-0200-000002000000}"/>
-    <hyperlink ref="D5" r:id="rId4" xr:uid="{00000000-0004-0000-0200-000003000000}"/>
-    <hyperlink ref="D6" r:id="rId5" xr:uid="{00000000-0004-0000-0200-000004000000}"/>
-    <hyperlink ref="D7" r:id="rId6" xr:uid="{00000000-0004-0000-0200-000005000000}"/>
-    <hyperlink ref="D8" r:id="rId7" xr:uid="{00000000-0004-0000-0200-000006000000}"/>
-    <hyperlink ref="D9" r:id="rId8" xr:uid="{00000000-0004-0000-0200-000007000000}"/>
-    <hyperlink ref="D10" r:id="rId9" xr:uid="{00000000-0004-0000-0200-000008000000}"/>
-    <hyperlink ref="D11" r:id="rId10" xr:uid="{00000000-0004-0000-0200-000009000000}"/>
-    <hyperlink ref="D12" r:id="rId11" xr:uid="{00000000-0004-0000-0200-00000A000000}"/>
-    <hyperlink ref="D13" r:id="rId12" xr:uid="{00000000-0004-0000-0200-00000B000000}"/>
-    <hyperlink ref="D14" r:id="rId13" xr:uid="{00000000-0004-0000-0200-00000C000000}"/>
-    <hyperlink ref="D15" r:id="rId14" xr:uid="{00000000-0004-0000-0200-00000D000000}"/>
-    <hyperlink ref="D16" r:id="rId15" xr:uid="{00000000-0004-0000-0200-00000E000000}"/>
-    <hyperlink ref="D17" r:id="rId16" xr:uid="{00000000-0004-0000-0200-00000F000000}"/>
-    <hyperlink ref="D18" r:id="rId17" xr:uid="{00000000-0004-0000-0200-000010000000}"/>
-    <hyperlink ref="D19" r:id="rId18" xr:uid="{00000000-0004-0000-0200-000011000000}"/>
-    <hyperlink ref="D20" r:id="rId19" xr:uid="{00000000-0004-0000-0200-000012000000}"/>
-    <hyperlink ref="D21" r:id="rId20" xr:uid="{00000000-0004-0000-0200-000013000000}"/>
-    <hyperlink ref="D22" r:id="rId21" xr:uid="{00000000-0004-0000-0200-000014000000}"/>
-    <hyperlink ref="D23" r:id="rId22" xr:uid="{00000000-0004-0000-0200-000015000000}"/>
-    <hyperlink ref="D24" r:id="rId23" xr:uid="{00000000-0004-0000-0200-000016000000}"/>
-    <hyperlink ref="D25" r:id="rId24" xr:uid="{00000000-0004-0000-0200-000017000000}"/>
-    <hyperlink ref="D26" r:id="rId25" xr:uid="{00000000-0004-0000-0200-000018000000}"/>
-    <hyperlink ref="D27" r:id="rId26" xr:uid="{00000000-0004-0000-0200-000019000000}"/>
-    <hyperlink ref="D28" r:id="rId27" xr:uid="{00000000-0004-0000-0200-00001A000000}"/>
-    <hyperlink ref="D29" r:id="rId28" xr:uid="{00000000-0004-0000-0200-00001B000000}"/>
-    <hyperlink ref="D30" r:id="rId29" xr:uid="{00000000-0004-0000-0200-00001C000000}"/>
-    <hyperlink ref="D31" r:id="rId30" xr:uid="{00000000-0004-0000-0200-00001D000000}"/>
-    <hyperlink ref="D32" r:id="rId31" xr:uid="{00000000-0004-0000-0200-00001E000000}"/>
-    <hyperlink ref="D33" r:id="rId32" xr:uid="{00000000-0004-0000-0200-00001F000000}"/>
-    <hyperlink ref="D34" r:id="rId33" xr:uid="{00000000-0004-0000-0200-000020000000}"/>
-    <hyperlink ref="D35" r:id="rId34" xr:uid="{00000000-0004-0000-0200-000021000000}"/>
-    <hyperlink ref="D36" r:id="rId35" xr:uid="{00000000-0004-0000-0200-000022000000}"/>
-    <hyperlink ref="D37" r:id="rId36" xr:uid="{00000000-0004-0000-0200-000023000000}"/>
-    <hyperlink ref="D38" r:id="rId37" xr:uid="{00000000-0004-0000-0200-000024000000}"/>
-    <hyperlink ref="D39" r:id="rId38" xr:uid="{00000000-0004-0000-0200-000025000000}"/>
-    <hyperlink ref="D40" r:id="rId39" xr:uid="{00000000-0004-0000-0200-000026000000}"/>
-    <hyperlink ref="D41" r:id="rId40" xr:uid="{00000000-0004-0000-0200-000027000000}"/>
-    <hyperlink ref="D42" r:id="rId41" xr:uid="{00000000-0004-0000-0200-000028000000}"/>
-    <hyperlink ref="D43" r:id="rId42" xr:uid="{00000000-0004-0000-0200-000029000000}"/>
-    <hyperlink ref="D44" r:id="rId43" xr:uid="{00000000-0004-0000-0200-00002A000000}"/>
-    <hyperlink ref="D45" r:id="rId44" xr:uid="{00000000-0004-0000-0200-00002B000000}"/>
-    <hyperlink ref="D46" r:id="rId45" xr:uid="{00000000-0004-0000-0200-00002C000000}"/>
-    <hyperlink ref="D47" r:id="rId46" xr:uid="{00000000-0004-0000-0200-00002D000000}"/>
+    <hyperlink ref="D5" r:id="rId3" xr:uid="{00000000-0004-0000-0200-000003000000}"/>
+    <hyperlink ref="D6" r:id="rId4" xr:uid="{00000000-0004-0000-0200-000004000000}"/>
+    <hyperlink ref="D7" r:id="rId5" xr:uid="{00000000-0004-0000-0200-000005000000}"/>
+    <hyperlink ref="D8" r:id="rId6" xr:uid="{00000000-0004-0000-0200-000006000000}"/>
+    <hyperlink ref="D9" r:id="rId7" xr:uid="{00000000-0004-0000-0200-000007000000}"/>
+    <hyperlink ref="D10" r:id="rId8" xr:uid="{00000000-0004-0000-0200-000008000000}"/>
+    <hyperlink ref="D11" r:id="rId9" xr:uid="{00000000-0004-0000-0200-000009000000}"/>
+    <hyperlink ref="D12" r:id="rId10" xr:uid="{00000000-0004-0000-0200-00000A000000}"/>
+    <hyperlink ref="D13" r:id="rId11" xr:uid="{00000000-0004-0000-0200-00000B000000}"/>
+    <hyperlink ref="D14" r:id="rId12" xr:uid="{00000000-0004-0000-0200-00000C000000}"/>
+    <hyperlink ref="D15" r:id="rId13" xr:uid="{00000000-0004-0000-0200-00000D000000}"/>
+    <hyperlink ref="D16" r:id="rId14" xr:uid="{00000000-0004-0000-0200-00000E000000}"/>
+    <hyperlink ref="D17" r:id="rId15" xr:uid="{00000000-0004-0000-0200-00000F000000}"/>
+    <hyperlink ref="D18" r:id="rId16" xr:uid="{00000000-0004-0000-0200-000010000000}"/>
+    <hyperlink ref="D19" r:id="rId17" xr:uid="{00000000-0004-0000-0200-000011000000}"/>
+    <hyperlink ref="D20" r:id="rId18" xr:uid="{00000000-0004-0000-0200-000012000000}"/>
+    <hyperlink ref="D21" r:id="rId19" xr:uid="{00000000-0004-0000-0200-000013000000}"/>
+    <hyperlink ref="D22" r:id="rId20" xr:uid="{00000000-0004-0000-0200-000014000000}"/>
+    <hyperlink ref="D23" r:id="rId21" xr:uid="{00000000-0004-0000-0200-000015000000}"/>
+    <hyperlink ref="D24" r:id="rId22" xr:uid="{00000000-0004-0000-0200-000016000000}"/>
+    <hyperlink ref="D25" r:id="rId23" xr:uid="{00000000-0004-0000-0200-000017000000}"/>
+    <hyperlink ref="D26" r:id="rId24" xr:uid="{00000000-0004-0000-0200-000018000000}"/>
+    <hyperlink ref="D27" r:id="rId25" xr:uid="{00000000-0004-0000-0200-000019000000}"/>
+    <hyperlink ref="D28" r:id="rId26" xr:uid="{00000000-0004-0000-0200-00001A000000}"/>
+    <hyperlink ref="D29" r:id="rId27" xr:uid="{00000000-0004-0000-0200-00001B000000}"/>
+    <hyperlink ref="D30" r:id="rId28" xr:uid="{00000000-0004-0000-0200-00001C000000}"/>
+    <hyperlink ref="D31" r:id="rId29" xr:uid="{00000000-0004-0000-0200-00001D000000}"/>
+    <hyperlink ref="D32" r:id="rId30" xr:uid="{00000000-0004-0000-0200-00001E000000}"/>
+    <hyperlink ref="D33" r:id="rId31" xr:uid="{00000000-0004-0000-0200-00001F000000}"/>
+    <hyperlink ref="D34" r:id="rId32" xr:uid="{00000000-0004-0000-0200-000020000000}"/>
+    <hyperlink ref="D35" r:id="rId33" xr:uid="{00000000-0004-0000-0200-000021000000}"/>
+    <hyperlink ref="D36" r:id="rId34" xr:uid="{00000000-0004-0000-0200-000022000000}"/>
+    <hyperlink ref="D37" r:id="rId35" xr:uid="{00000000-0004-0000-0200-000023000000}"/>
+    <hyperlink ref="D38" r:id="rId36" xr:uid="{00000000-0004-0000-0200-000024000000}"/>
+    <hyperlink ref="D39" r:id="rId37" xr:uid="{00000000-0004-0000-0200-000025000000}"/>
+    <hyperlink ref="D40" r:id="rId38" xr:uid="{00000000-0004-0000-0200-000026000000}"/>
+    <hyperlink ref="D41" r:id="rId39" xr:uid="{00000000-0004-0000-0200-000027000000}"/>
+    <hyperlink ref="D42" r:id="rId40" xr:uid="{00000000-0004-0000-0200-000028000000}"/>
+    <hyperlink ref="D43" r:id="rId41" xr:uid="{00000000-0004-0000-0200-000029000000}"/>
+    <hyperlink ref="D44" r:id="rId42" xr:uid="{00000000-0004-0000-0200-00002A000000}"/>
+    <hyperlink ref="D45" r:id="rId43" xr:uid="{00000000-0004-0000-0200-00002B000000}"/>
+    <hyperlink ref="D46" r:id="rId44" xr:uid="{00000000-0004-0000-0200-00002C000000}"/>
+    <hyperlink ref="D47" r:id="rId45" xr:uid="{00000000-0004-0000-0200-00002D000000}"/>
+    <hyperlink ref="D4" r:id="rId46" display="https://sdisgovco.sharepoint.com/:w:/r/sites/SubdireccindeJuventudPoliticaPblica/Documentos%20compartidos/Anal%C3%ADtica%20e%20Innovaci%C3%B3n/Gestor%20de%20conocimiento/enlaces/Documentaci%C3%B3n%20JCO/02_JCO_instructivo_pago/20240308_ins_pss_125_v0_instructivo_pagos_parceros.docx?d=wd102df19a9164946a456beea1927b4da&amp;csf=1&amp;web=1&amp;e=sp7lh2" xr:uid="{00000000-0004-0000-0200-000002000000}"/>
+    <hyperlink ref="D51" r:id="rId47" display="https://sdisgovco.sharepoint.com/:b:/r/sites/SubdireccindeJuventudPoliticaPblica/Documentos%20compartidos/Anal%C3%ADtica%20e%20Innovaci%C3%B3n/Gestor%20de%20conocimiento/enlaces/Documentaci%C3%B3n%20JCO/07_Parceros_convenios/convenio_10907_2021/000.%20Estudios%20Previos%20IDIPRON%20-%20SDIS_REVPOB.pdf?csf=1&amp;web=1&amp;e=i1m9Wz" xr:uid="{07FD4743-D59F-49A8-BA56-3024640E466F}"/>
+    <hyperlink ref="D53" r:id="rId48" display="https://sdisgovco.sharepoint.com/:b:/r/sites/SubdireccindeJuventudPoliticaPblica/Documentos%20compartidos/Anal%C3%ADtica%20e%20Innovaci%C3%B3n/Gestor%20de%20conocimiento/enlaces/Documentaci%C3%B3n%20JCO/07_Parceros_convenios/convenio_10907_2021/004.%20Minuta%20Convenio.pdf?csf=1&amp;web=1&amp;e=rNXqhi" xr:uid="{462FA3F5-F267-4229-BC22-B57B92C26433}"/>
+    <hyperlink ref="D52" r:id="rId49" display="https://sdisgovco.sharepoint.com/:b:/r/sites/SubdireccindeJuventudPoliticaPblica/Documentos%20compartidos/Anal%C3%ADtica%20e%20Innovaci%C3%B3n/Gestor%20de%20conocimiento/enlaces/Documentaci%C3%B3n%20JCO/07_Parceros_convenios/convenio_10907_2021/001.%20Anexo%20Tecnico%20Convenio%2010907-2021.pdf?csf=1&amp;web=1&amp;e=JY3rCR" xr:uid="{6C591704-7541-4F60-837F-903588848902}"/>
+    <hyperlink ref="D54" r:id="rId50" display="https://sdisgovco.sharepoint.com/:b:/r/sites/SubdireccindeJuventudPoliticaPblica/Documentos%20compartidos/Anal%C3%ADtica%20e%20Innovaci%C3%B3n/Gestor%20de%20conocimiento/enlaces/Documentaci%C3%B3n%20JCO/07_Parceros_convenios/convenio_5714_2023/C_PROCESO_23-22-62415_01002009_118807585.pdf?csf=1&amp;web=1&amp;e=LoGhSz" xr:uid="{2E84DC40-F2FB-43E7-91E4-FEC7EB16645E}"/>
+    <hyperlink ref="D49" r:id="rId51" display="https://sdisgovco.sharepoint.com/:b:/r/sites/SubdireccindeJuventudPoliticaPblica/Documentos%20compartidos/Anal%C3%ADtica%20e%20Innovaci%C3%B3n/Gestor%20de%20conocimiento/enlaces/Documentaci%C3%B3n%20JCO/07_Parceros_convenios/convenio_8336_2021/ALUMA_PROCESO_21-22-26707_01002009_130655716.pdf?csf=1&amp;web=1&amp;e=JgNTkN" xr:uid="{654637A8-CBFD-4FCB-8084-12C2C25F732B}"/>
+    <hyperlink ref="D50" r:id="rId52" display="https://sdisgovco.sharepoint.com/:b:/r/sites/SubdireccindeJuventudPoliticaPblica/Documentos%20compartidos/Anal%C3%ADtica%20e%20Innovaci%C3%B3n/Gestor%20de%20conocimiento/enlaces/Documentaci%C3%B3n%20JCO/07_Parceros_convenios/convenio_8336_2021/C_PROCESO_21-22-26707_01002009_90251312.pdf?csf=1&amp;web=1&amp;e=MTsOli" xr:uid="{3E1995A5-01A8-457E-883F-B54A94D290EE}"/>
+    <hyperlink ref="D56" r:id="rId53" display="https://sdisgovco.sharepoint.com/:b:/r/sites/SubdireccindeJuventudPoliticaPblica/Documentos%20compartidos/Anal%C3%ADtica%20e%20Innovaci%C3%B3n/Gestor%20de%20conocimiento/enlaces/Documentaci%C3%B3n%20JCO/08_Parceros_mesa_GIS/%2310%20ACTA%20MESA%20GIS%2013102022.Firmado.pdf?csf=1&amp;web=1&amp;e=dzUZ3a" xr:uid="{955DBC9E-D3D3-4462-82D6-4D9105DFDB0E}"/>
+    <hyperlink ref="D55" r:id="rId54" display="https://sdisgovco.sharepoint.com/:b:/r/sites/SubdireccindeJuventudPoliticaPblica/Documentos%20compartidos/Anal%C3%ADtica%20e%20Innovaci%C3%B3n/Gestor%20de%20conocimiento/enlaces/Documentaci%C3%B3n%20JCO/08_Parceros_mesa_GIS/ACTA%20Mesa%20GIs%2014092021.pdf?csf=1&amp;web=1&amp;e=uEBfrO" xr:uid="{CD7A6961-D3BE-4431-872E-A7478D023273}"/>
+    <hyperlink ref="D57" r:id="rId55" display="https://sdisgovco.sharepoint.com/:b:/r/sites/SubdireccindeJuventudPoliticaPblica/Documentos%20compartidos/Anal%C3%ADtica%20e%20Innovaci%C3%B3n/Gestor%20de%20conocimiento/enlaces/Documentaci%C3%B3n%20JCO/08_Parceros_mesa_GIS/ACTA%20MESA%20GIS%20no.%203%2011-OCT-23.pdf?csf=1&amp;web=1&amp;e=aELNxY" xr:uid="{5F5F31D7-0AEA-4988-9BCD-9CD6D38F7C83}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2948,14 +3032,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="138.9296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="96.3984375" customWidth="1"/>
+    <col min="1" max="1" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="139" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="96.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -2966,7 +3050,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2977,7 +3061,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -2988,7 +3072,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -2999,7 +3083,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -3010,7 +3094,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -3021,7 +3105,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>16</v>
       </c>
